--- a/docs/source/tutorials/tutorial_simple/model/sets.xlsx
+++ b/docs/source/tutorials/tutorial_simple/model/sets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git_repos\pyesm\tests\models\integrated\1_coupled_model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\cvxlab\docs\source\tutorials\tutorial_simple\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C03F03-3BF8-4C9E-8F3F-7D536CBB7A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711C8911-29A3-464B-B235-A72F53430F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2350" yWindow="2250" windowWidth="14760" windowHeight="15370" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5440" yWindow="2360" windowWidth="23460" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_set_RESOURCES" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>resources_Name</t>
   </si>
@@ -30,16 +30,10 @@
     <t>products_Name</t>
   </si>
   <si>
-    <t>products_Aggregation</t>
-  </si>
-  <si>
     <t>product_data_Name</t>
   </si>
   <si>
     <t>product_data_category</t>
-  </si>
-  <si>
-    <t>product_data_Aggregation</t>
   </si>
   <si>
     <t>low energy</t>
@@ -445,17 +439,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -465,70 +459,64 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
